--- a/data/burst speed/jess wheeler/sent from jess/raw/02.21.10 combined.xlsx
+++ b/data/burst speed/jess wheeler/sent from jess/raw/02.21.10 combined.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10703"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Drosophila wind tunnel/data/burst speed/jess wheeler/sent from jess/raw/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/wind-tunnel-flies/data/burst speed/jess wheeler/sent from jess/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0163CC9C-8D6C-5247-9E88-B25738022C36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31D5722F-AB3A-AD40-B3EF-05FF428FBD59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6920" yWindow="600" windowWidth="21520" windowHeight="15840" xr2:uid="{9A9CBB1F-9929-E04F-9B9A-AF787C2B120B}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="130">
   <si>
     <t xml:space="preserve"> </t>
   </si>
@@ -409,6 +409,9 @@
   </si>
   <si>
     <t>aa2m25.02.21.10-01</t>
+  </si>
+  <si>
+    <t>not sure if this is 6 of one fly or if its two flies with same id</t>
   </si>
 </sst>
 </file>
@@ -3967,6 +3970,9 @@
       <c r="E288" s="1" t="s">
         <v>90</v>
       </c>
+      <c r="F288" s="1" t="s">
+        <v>129</v>
+      </c>
     </row>
     <row r="289" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A289" s="1" t="s">
